--- a/19/4.1 ML Projects/2.Projects/Final_Regression_01/Data_Train_Test/y_train_true.xlsx
+++ b/19/4.1 ML Projects/2.Projects/Final_Regression_01/Data_Train_Test/y_train_true.xlsx
@@ -425,781 +425,493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:A97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Salary</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
         <v>78100</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" t="n">
         <v>146000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B4" t="n">
+      <c r="A4" t="n">
         <v>98500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" t="n">
         <v>167400</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" t="n">
         <v>126200</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B8" t="n">
+      <c r="A8" t="n">
         <v>94700</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B9" t="n">
+      <c r="A9" t="n">
         <v>129600</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B10" t="n">
+      <c r="A10" t="n">
         <v>110600</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B11" t="n">
+      <c r="A11" t="n">
         <v>146800</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B12" t="n">
+      <c r="A12" t="n">
         <v>93300</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B13" t="n">
+      <c r="A13" t="n">
         <v>28000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B14" t="n">
+      <c r="A14" t="n">
         <v>142400</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B15" t="n">
+      <c r="A15" t="n">
         <v>155300</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B16" t="n">
+      <c r="A16" t="n">
         <v>65000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" t="n">
+      <c r="A17" t="n">
         <v>152800</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B18" t="n">
+      <c r="A18" t="n">
         <v>157800</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B19" t="n">
+      <c r="A19" t="n">
         <v>131000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B20" t="n">
+      <c r="A20" t="n">
         <v>235200</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B21" t="n">
+      <c r="A21" t="n">
         <v>122800</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B22" t="n">
+      <c r="A22" t="n">
         <v>117800</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B23" t="n">
+      <c r="A23" t="n">
         <v>111100</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" t="n">
+      <c r="A24" t="n">
         <v>93100</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B25" t="n">
+      <c r="A25" t="n">
         <v>76700</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B26" t="n">
+      <c r="A26" t="n">
         <v>81300</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B27" t="n">
+      <c r="A27" t="n">
         <v>115300</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B28" t="n">
+      <c r="A28" t="n">
         <v>81700</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B29" t="n">
+      <c r="A29" t="n">
         <v>134100</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B30" t="n">
+      <c r="A30" t="n">
         <v>106300</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B31" t="n">
+      <c r="A31" t="n">
         <v>70700</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B32" t="n">
+      <c r="A32" t="n">
         <v>218200</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="B33" t="n">
+      <c r="A33" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B34" t="n">
+      <c r="A34" t="n">
         <v>162400</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B35" t="n">
+      <c r="A35" t="n">
         <v>168900</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B36" t="n">
+      <c r="A36" t="n">
         <v>97900</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B37" t="n">
+      <c r="A37" t="n">
         <v>136800</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B38" t="n">
+      <c r="A38" t="n">
         <v>109400</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B39" t="n">
+      <c r="A39" t="n">
         <v>139200</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B40" t="n">
+      <c r="A40" t="n">
         <v>107000</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B41" t="n">
+      <c r="A41" t="n">
         <v>118200</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B42" t="n">
+      <c r="A42" t="n">
         <v>310000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B43" t="n">
+      <c r="A43" t="n">
         <v>118500</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B44" t="n">
+      <c r="A44" t="n">
         <v>100400</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B45" t="n">
+      <c r="A45" t="n">
         <v>101200</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" t="n">
+      <c r="A46" t="n">
         <v>137200</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B47" t="n">
+      <c r="A47" t="n">
         <v>115100</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B48" t="n">
+      <c r="A48" t="n">
         <v>134700</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B49" t="n">
+      <c r="A49" t="n">
         <v>25000</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B50" t="n">
+      <c r="A50" t="n">
         <v>65600</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B51" t="n">
+      <c r="A51" t="n">
         <v>77000</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B52" t="n">
+      <c r="A52" t="n">
         <v>32500</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B53" t="n">
+      <c r="A53" t="n">
         <v>131100</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B54" t="n">
+      <c r="A54" t="n">
         <v>126300</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B55" t="n">
+      <c r="A55" t="n">
         <v>239300</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B56" t="n">
+      <c r="A56" t="n">
         <v>169900</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B57" t="n">
+      <c r="A57" t="n">
         <v>109800</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B58" t="n">
+      <c r="A58" t="n">
         <v>104700</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B59" t="n">
+      <c r="A59" t="n">
         <v>96600</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B60" t="n">
+      <c r="A60" t="n">
         <v>80000</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B61" t="n">
+      <c r="A61" t="n">
         <v>92700</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B62" t="n">
+      <c r="A62" t="n">
         <v>133300</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B63" t="n">
+      <c r="A63" t="n">
         <v>99400</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B64" t="n">
+      <c r="A64" t="n">
         <v>93100</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B65" t="n">
+      <c r="A65" t="n">
         <v>138200</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B66" t="n">
+      <c r="A66" t="n">
         <v>480000</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B67" t="n">
+      <c r="A67" t="n">
         <v>98000</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B68" t="n">
+      <c r="A68" t="n">
         <v>151300</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B69" t="n">
+      <c r="A69" t="n">
         <v>87800</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B70" t="n">
+      <c r="A70" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B71" t="n">
+      <c r="A71" t="n">
         <v>119200</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B72" t="n">
+      <c r="A72" t="n">
         <v>98300</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B73" t="n">
+      <c r="A73" t="n">
         <v>395000</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B74" t="n">
+      <c r="A74" t="n">
         <v>71400</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B75" t="n">
+      <c r="A75" t="n">
         <v>95100</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B76" t="n">
+      <c r="A76" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B77" t="n">
+      <c r="A77" t="n">
         <v>212200</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B78" t="n">
+      <c r="A78" t="n">
         <v>171800</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B79" t="n">
+      <c r="A79" t="n">
         <v>113800</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B80" t="n">
+      <c r="A80" t="n">
         <v>139400</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B81" t="n">
+      <c r="A81" t="n">
         <v>111000</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B82" t="n">
+      <c r="A82" t="n">
         <v>290000</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B83" t="n">
+      <c r="A83" t="n">
         <v>89600</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B84" t="n">
+      <c r="A84" t="n">
         <v>145500</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B85" t="n">
+      <c r="A85" t="n">
         <v>380000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B86" t="n">
+      <c r="A86" t="n">
         <v>142800</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="n">
+      <c r="A87" t="n">
         <v>159100</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B88" t="n">
+      <c r="A88" t="n">
         <v>121700</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B89" t="n">
+      <c r="A89" t="n">
         <v>58000</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B90" t="n">
+      <c r="A90" t="n">
         <v>151000</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B91" t="n">
+      <c r="A91" t="n">
         <v>119900</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B92" t="n">
+      <c r="A92" t="n">
         <v>72100</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B93" t="n">
+      <c r="A93" t="n">
         <v>40000</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B94" t="n">
+      <c r="A94" t="n">
         <v>76900</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B95" t="n">
+      <c r="A95" t="n">
         <v>168900</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B96" t="n">
+      <c r="A96" t="n">
         <v>149700</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B97" t="n">
+      <c r="A97" t="n">
         <v>55000</v>
       </c>
     </row>
